--- a/output/graficos_dimensiones/comunal_e_mediabrut_a_2021_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mediabrut_a_2021_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-28 00:42</t>
+    <t xml:space="preserve">2026-08-17 15:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mediabrut_a_2021_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mediabrut_a_2021_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 15:35</t>
+    <t xml:space="preserve">2026-08-17 21:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mediabrut_a_2021_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mediabrut_a_2021_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 21:28</t>
+    <t xml:space="preserve">2026-09-06 21:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
